--- a/erp-server/erp-server-wms/src/main/resources/excel/supplierInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/supplierInventory.xlsx
@@ -71,7 +71,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.salestateName}</t>
+    <t>{.saletateName}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/supplierInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/supplierInventory.xlsx
@@ -71,7 +71,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.saletateName}</t>
+    <t>{.saleStateName}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>
